--- a/cost-plans/Primary-School-Expansion.xlsx
+++ b/cost-plans/Primary-School-Expansion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\qs\project-cost-control\cost-plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5209AD51-9B1B-4B12-BAF6-8A2D91FEE277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0438F16F-0499-4AC8-8783-558824BABBD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14092" activeTab="1" xr2:uid="{0C8C6BE1-598D-4333-9AA5-A074653745B1}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14092" activeTab="2" xr2:uid="{0C8C6BE1-598D-4333-9AA5-A074653745B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Cost Plan" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
   <si>
     <t>Project Name</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>Primary School Expansion — Cost Value Reconciliation</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Education</t>
   </si>
 </sst>
 </file>
@@ -494,15 +500,15 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="1" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="4" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="4" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="37" fontId="1" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="37" fontId="4" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="37" fontId="4" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Accent1" xfId="1" builtinId="29"/>
@@ -2022,33 +2028,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="35.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="49" t="str">
+      <c r="A2" s="52" t="str">
         <f ca="1">"Meridian Cost Consultants | Report Date: "&amp;TEXT(TODAY(),"DD MMMM YYYY")</f>
-        <v>Meridian Cost Consultants | Report Date: 15 May 2026</v>
-      </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
+        <v>Meridian Cost Consultants | Report Date: 16 May 2026</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
@@ -2113,7 +2119,7 @@
         <f>SUM(H6:H7)</f>
         <v>294000</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="48">
         <f>E5-H5</f>
         <v>0</v>
       </c>
@@ -2146,7 +2152,7 @@
       <c r="H6" s="34">
         <v>168000</v>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="49">
         <f t="shared" ref="I6:I23" si="2">E6-H6</f>
         <v>0</v>
       </c>
@@ -2178,7 +2184,7 @@
       <c r="H7" s="35">
         <v>126000</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="50">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2217,7 +2223,7 @@
         <f t="shared" si="3"/>
         <v>1120000</v>
       </c>
-      <c r="I8" s="50">
+      <c r="I8" s="48">
         <f>E8-H8</f>
         <v>0</v>
       </c>
@@ -2250,7 +2256,7 @@
       <c r="H9" s="34">
         <v>378000</v>
       </c>
-      <c r="I9" s="51">
+      <c r="I9" s="49">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2282,7 +2288,7 @@
       <c r="H10" s="35">
         <v>252000</v>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="50">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2316,7 +2322,7 @@
       <c r="H11" s="34">
         <v>322000</v>
       </c>
-      <c r="I11" s="51">
+      <c r="I11" s="49">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2348,7 +2354,7 @@
       <c r="H12" s="35">
         <v>168000</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12" s="50">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2387,7 +2393,7 @@
         <f t="shared" si="4"/>
         <v>504000</v>
       </c>
-      <c r="I13" s="50">
+      <c r="I13" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2420,7 +2426,7 @@
       <c r="H14" s="34">
         <v>168000</v>
       </c>
-      <c r="I14" s="51">
+      <c r="I14" s="49">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2452,7 +2458,7 @@
       <c r="H15" s="35">
         <v>210000</v>
       </c>
-      <c r="I15" s="52">
+      <c r="I15" s="50">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2484,7 +2490,7 @@
       <c r="H16" s="34">
         <v>126000</v>
       </c>
-      <c r="I16" s="51">
+      <c r="I16" s="49">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2516,7 +2522,7 @@
       <c r="H17" s="33">
         <v>210000</v>
       </c>
-      <c r="I17" s="50">
+      <c r="I17" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2555,7 +2561,7 @@
         <f t="shared" si="5"/>
         <v>816000</v>
       </c>
-      <c r="I18" s="50">
+      <c r="I18" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2588,7 +2594,7 @@
       <c r="H19" s="34">
         <v>462000</v>
       </c>
-      <c r="I19" s="51">
+      <c r="I19" s="49">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2622,7 +2628,7 @@
       <c r="H20" s="35">
         <v>354000</v>
       </c>
-      <c r="I20" s="52">
+      <c r="I20" s="50">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2656,7 +2662,7 @@
       <c r="H21" s="33">
         <v>284000</v>
       </c>
-      <c r="I21" s="50">
+      <c r="I21" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2688,7 +2694,7 @@
       <c r="H22" s="33">
         <v>882000</v>
       </c>
-      <c r="I22" s="50">
+      <c r="I22" s="48">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2720,7 +2726,7 @@
       <c r="H23" s="33">
         <v>0</v>
       </c>
-      <c r="I23" s="50">
+      <c r="I23" s="48">
         <f t="shared" si="2"/>
         <v>168000</v>
       </c>
@@ -2737,7 +2743,7 @@
         <v>4200000</v>
       </c>
       <c r="D24" s="36">
-        <f t="shared" ref="D24:J24" si="6">SUM(D5,D8,D13,D17,D18,D23,D21,D22)</f>
+        <f t="shared" ref="D24:I24" si="6">SUM(D5,D8,D13,D17,D18,D23,D21,D22)</f>
         <v>78000</v>
       </c>
       <c r="E24" s="36">
@@ -2803,26 +2809,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="35.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="37" t="s">
@@ -3156,7 +3162,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2FB73FC-2423-441D-B32D-DF5AF30B74F5}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.69140625" bestFit="1" customWidth="1"/>
@@ -3236,6 +3242,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
